--- a/assets/docs/lop1/KHDH ca khoi - Lop 1.xlsx
+++ b/assets/docs/lop1/KHDH ca khoi - Lop 1.xlsx
@@ -632,7 +632,12 @@
           <t>7 – 9</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Khám phá của bài “LÀM QUEN VỚI CÁC NÉT CƠ BẢN, CÁC CHỮ SỐ, BẢNG CHỮ CÁI VÀ DẤU THANH”
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở hoạt động Luyện tập, GV mở bài tập tương tác trên máy chiếu: các nét, chữ số và dấu thanh lẫn lộn</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -731,7 +736,12 @@
           <t>15 – 16</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Khám phá của bài “B, b, DẤU HUYỀN”, GV chiếu tranh nhận biết phóng to, mở bản đọc mẫu câu Bà cho bé búp bê và bản phát âm mẫu âm…
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở phần đọc tiếng, GV mở bài tập tương tác: tiếng ba trên màn hình, khi GV kéo dấu huyền đặt lên chữ a thì tiếng đổi thành bà và máy đọc lên</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -761,7 +771,12 @@
           <t>17 – 18</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Khám phá của bài “C, c, DẤU SẮC”, GV chiếu tranh nhận biết phóng to, mở bản đọc mẫu câu Nam và bố câu cá và bản phát âm mẫu âm…
+Năng lực số Miền 2 (Cơ bản, bậc 1): Ở phần luyện nói, GV mở clip ngắn cảnh HS chào cô giáo, chào bạn khi vào lớp và khi ra về; HS xem, nhắc lại lời chào rồi đóng vai theo nhóm đôi</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -791,7 +806,12 @@
           <t>19 – 20</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Khám phá của bài “E, e, Ê, ê”, GV chiếu tranh nhận biết phóng to, mở bản đọc mẫu câu Bé kể mẹ nghe về bạn bè và bản phát âm…
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở phần đọc tiếng, GV mở bài tập tương tác: chữ e trên màn hình, khi GV kéo dấu mũ đặt lên thì thành ê và máy đọc lên; HS quan sát</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -891,7 +911,8 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Chiếu phóng to tranh nhận biết “Đàn bò gặm cỏ” của bài chữ o và dấu hỏi, chỉ vào từng con vật, ngọn cỏ.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh nhận biết “Đàn bò gặm cỏ” của bài chữ o và dấu hỏi, chỉ vào từng con vật, ngọn cỏ để HS nói nội dung tranh
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở bài tập tương tác nối tiếng bò, cò, cỏ với đúng hình; máy báo đúng, sai ngay nên HS tự nhận ra mình còn lẫn tiếng có dấu hỏi với tiếng không…</t>
         </is>
       </c>
     </row>
@@ -953,7 +974,12 @@
           <t>29 – 30</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh nhận biết “Dưới gốc đa, các bạn chơi dung dăng dung dẻ” của bài chữ d, đ, kèm ảnh thật con dê, bến đò, hòn đá
+Năng lực số Miền 3 (Cơ bản, bậc 1): GV viết mẫu chữ d, đ trên bảng tương tác theo từng nét, tô lại nét mà HS hay viết sai; vài em lên viết thử chữ d</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -1083,7 +1109,8 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 1): Mở bài tập tương tác nối tiếng có chữ i, chữ k.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh nhận biết của bài chữ i, k để HS gọi tên người, vật trong tranh và nói nhân vật đang làm gì
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở bài tập tương tác nối tiếng có chữ i, chữ k với hình tương ứng; máy báo đúng, sai ngay nên HS tự nhận ra mình còn lẫn hai chữ này</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1142,12 @@
           <t>39 – 40</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr"/>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh nhận biết của bài chữ h, l, chỉ vào từng chi tiết để HS kể lại việc các nhân vật đang làm
+Năng lực số Miền 2 (Cơ bản, bậc 1): GV ghi âm lượt đọc từ ngữ của vài HS rồi mở lại cho cả lớp nghe; các em nghe giọng mình</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -1145,7 +1177,12 @@
           <t>41 – 42</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr"/>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh nhận biết của bài chữ u, ư và hỏi tranh vẽ ai, đang làm gì; sau đó mở bản ghi âm đọc mẫu câu nhận biết theo từng cụm…
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở bài tập tương tác chọn tiếng viết đúng trong các cặp dễ lẫn giữa u và ư; máy báo đúng, sai ngay nên HS biết mình còn nhầm chỗ nào</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -1175,7 +1212,12 @@
           <t>43 – 44</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr"/>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh nhận biết của bài chữ ch, kh cùng ảnh thật vài sự vật có tiếng chứa ch, kh để HS gọi tên; nhờ ảnh lớn
+Năng lực số Miền 3 (Cơ bản, bậc 1): GV viết mẫu chữ ch, kh trên bảng tương tác theo từng nét, tô lại nét mà HS hay viết sai</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -1275,7 +1317,8 @@
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Chiếu phóng to tranh nhận biết của bài chữ m, n và hỏi tranh vẽ ai, đang làm gì.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh nhận biết của bài chữ m, n và hỏi tranh vẽ ai, đang làm gì; GV mở bản ghi âm phát âm mẫu m
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở bài tập tương tác nối tiếng có chữ m với hình và tiếng có chữ n với hình; máy báo đúng</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1384,12 @@
           <t>53 – 54</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr"/>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh nhận biết của bài chữ gh, nh, chỉ vào từng chi tiết để HS kể việc các nhân vật đang làm
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở bài tập tương tác chọn chữ đúng điền vào chỗ trống giữa g và gh; máy báo đúng, sai ngay nên HS tự rút ra quy tắc gh chỉ đứng trước e</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -1471,7 +1519,8 @@
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 1): Mở bài tập tương tác nối tiếng có r, có s với hình tương ứng; máy báo đúng, sai ngay nên.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh nhận biết của bài chữ r, s và hỏi tranh vẽ ai, đang làm gì; GV mở bản ghi âm phát âm mẫu r
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở bài tập tương tác nối tiếng có r, có s với hình tương ứng; máy báo đúng, sai ngay nên HS biết mình còn lẫn chỗ nào</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1612,12 @@
           <t>67 – 68</t>
         </is>
       </c>
-      <c r="H35" s="4" t="inlineStr"/>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh nhận biết của bài vần ua, ưa và ảnh thật vài sự vật có tiếng chứa hai vần này; HS gọi tên, tìm tiếng có ua
+Năng lực số Miền 3 (Cơ bản, bậc 1): GV viết mẫu vần ua, ưa trên bảng tương tác theo từng nét, tô lại dấu móc của chữ ư mà HS hay quên</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -1663,7 +1717,8 @@
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Chiếu phóng to tranh nhận biết của bài chữ ph, qu và hỏi tranh vẽ ai, đang làm gì.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh nhận biết của bài chữ ph, qu và hỏi tranh vẽ ai, đang làm gì; GV mở bản ghi âm phát âm mẫu ph
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở bài tập tương tác nối tiếng có ph, có qu với hình tương ứng; máy báo đúng, sai ngay nên HS tự nhận ra mình còn nhầm chỗ nào</t>
         </is>
       </c>
     </row>
@@ -1695,7 +1750,12 @@
           <t>75 – 76</t>
         </is>
       </c>
-      <c r="H39" s="4" t="inlineStr"/>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh nhận biết của bài chữ v, x cùng ảnh thật vài sự vật có tiếng chứa v, x để HS gọi tên
+Năng lực số Miền 2 (Cơ bản, bậc 1): GV ghi âm lượt đọc từ ngữ của vài HS rồi mở lại cho cả lớp nghe; các em nghe giọng mình</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -1725,7 +1785,12 @@
           <t>77 – 78</t>
         </is>
       </c>
-      <c r="H40" s="4" t="inlineStr"/>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh nhận biết của bài chữ y, chỉ vào từng chi tiết để HS kể việc các nhân vật đang làm
+Năng lực số Miền 3 (Cơ bản, bậc 1): GV viết mẫu chữ y trên bảng tương tác theo từng nét, tô lại nét khuyết dưới mà HS hay viết ngắn; vài em lên viết thử cho cả lớp nhận xét độ cao</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -1755,7 +1820,12 @@
           <t>79 – 80</t>
         </is>
       </c>
-      <c r="H41" s="4" t="inlineStr"/>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 5 (Cơ bản, bậc 1): Ở tiết luyện tập chính tả, GV dùng trò chơi học liệu tương tác cho HS chọn đúng c hay k, g hay gh, ng hay ngh điền vào chỗ trống; máy báo đúng
+Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu bảng quy tắc chính tả phóng to và bấm sáng dần từng dòng khi cả lớp đọc; HS nhìn bảng lớn để nhớ mặt chữ</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -1855,7 +1925,8 @@
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 1): Mở bài tập tương tác nối tiếng có vần an, ăn, ân.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh nhận biết của bài vần an, ăn, ân và hỏi tranh vẽ ai, đang làm gì
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở bài tập tương tác nối tiếng có vần an, ăn, ân với hình tương ứng; máy báo đúng, sai ngay nên HS tự nhận ra mình còn nhầm vần nào</t>
         </is>
       </c>
     </row>
@@ -1887,7 +1958,12 @@
           <t>87 – 88</t>
         </is>
       </c>
-      <c r="H45" s="4" t="inlineStr"/>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh nhận biết của bài vần on, ôn, ơn cùng ảnh thật vài sự vật có tiếng chứa ba vần này
+Năng lực số Miền 2 (Cơ bản, bậc 1): GV ghi âm lượt đọc từ ngữ của vài HS rồi mở lại cho cả lớp nghe; các em nghe giọng mình</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -1917,7 +1993,12 @@
           <t>89 – 90</t>
         </is>
       </c>
-      <c r="H46" s="4" t="inlineStr"/>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh nhận biết của bài vần en, ên, in, un, chỉ vào từng chi tiết để HS kể việc nhân vật đang làm
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở bài tập tương tác ghép âm đầu với bốn vần vừa học rồi nối tiếng với hình; máy báo đúng</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -2047,7 +2128,8 @@
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Chiếu phóng to tranh nhận biết của bài vần om, ôm, ơm và hỏi tranh vẽ ai, đang làm gì.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh nhận biết của bài vần om, ôm, ơm và hỏi tranh vẽ ai, đang làm gì
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở bài tập tương tác nối tiếng có vần om, ôm, ơm với hình tương ứng; máy báo đúng, sai ngay nên HS tự nhận ra mình còn nhầm vần nào</t>
         </is>
       </c>
     </row>
@@ -2079,7 +2161,12 @@
           <t>99 – 100</t>
         </is>
       </c>
-      <c r="H51" s="4" t="inlineStr"/>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh nhận biết của bài vần em, êm, im, um cùng ảnh thật vài sự vật có tiếng chứa các vần này; ảnh lớn giúp HS nhìn rõ mặt chữ
+Năng lực số Miền 2 (Cơ bản, bậc 1): GV ghi âm lượt đọc từ ngữ của vài HS rồi mở lại cho cả lớp nghe; các em nghe giọng mình</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
@@ -2109,7 +2196,12 @@
           <t>101 – 102</t>
         </is>
       </c>
-      <c r="H52" s="4" t="inlineStr"/>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh nhận biết của bài vần ai, ay, ây, chỉ vào từng chi tiết để HS kể việc nhân vật đang làm
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở bài tập tương tác chọn vần đúng điền vào chỗ trống giữa ay và ây; máy báo đúng, sai ngay nên HS nhận ra hai vần này khác nhau ở dấu mũ…</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -2139,7 +2231,12 @@
           <t>103 – 104</t>
         </is>
       </c>
-      <c r="H53" s="4" t="inlineStr"/>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh nhận biết của bài vần oi, ôi, ơi và ảnh thật vài sự vật có tiếng chứa ba vần; HS gọi tên
+Năng lực số Miền 3 (Cơ bản, bậc 1): GV viết mẫu vần oi, ôi, ơi trên bảng tương tác theo từng nét, tô lại dấu mũ và dấu móc mà HS hay quên</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
@@ -2239,7 +2336,8 @@
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 1): Mở bài tập tương tác nối tiếng có vần ui, ưi.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh nhận biết của bài vần ui, ưi và hỏi tranh vẽ ai, đang làm gì; GV mở bản ghi âm đọc mẫu hai vần cho HS nghe rồi nhìn…
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở bài tập tương tác nối tiếng có vần ui, ưi với hình tương ứng; máy báo đúng, sai ngay nên HS tự nhận ra mình còn nhầm vần nào</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2399,12 @@
           <t>113 – 114</t>
         </is>
       </c>
-      <c r="H58" s="4" t="inlineStr"/>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh nhận biết của bài vần au, âu, êu, chỉ vào từng chi tiết để HS kể việc nhân vật đang làm
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở bài tập tương tác chọn vần đúng điền vào chỗ trống giữa au và âu; máy báo đúng, sai ngay nên HS nhận ra hai vần chỉ khác nhau ở dấu mũ</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -2331,7 +2434,12 @@
           <t>115 – 116</t>
         </is>
       </c>
-      <c r="H59" s="4" t="inlineStr"/>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh nhận biết của bài vần iu, ưu và ảnh thật vài sự vật có tiếng chứa hai vần; HS gọi tên
+Năng lực số Miền 3 (Cơ bản, bậc 1): GV viết mẫu vần iu, ưu trên bảng tương tác theo từng nét, tô lại dấu móc của chữ ư mà HS hay quên</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -2463,7 +2571,12 @@
           <t>123 – 124</t>
         </is>
       </c>
-      <c r="H63" s="4" t="inlineStr"/>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh nhận biết của bài vần oc, ôc, uc, ưc cùng ảnh thật vài sự vật có tiếng chứa các vần này; ảnh lớn giúp HS gọi tên sự vật
+Năng lực số Miền 2 (Cơ bản, bậc 1): GV ghi âm lượt đọc từ ngữ của vài HS rồi mở lại cho cả lớp nghe; các em nghe giọng mình</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -2493,7 +2606,12 @@
           <t>125 – 126</t>
         </is>
       </c>
-      <c r="H64" s="4" t="inlineStr"/>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh nhận biết của bài vần at, ăt, ât, chỉ vào từng chi tiết để HS kể việc nhân vật đang làm
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở bài tập tương tác chọn vần đúng điền vào chỗ trống giữa at, ăt và ât; máy báo đúng, sai ngay nên HS nhận ra ba vần chỉ khác nhau ở dấu</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -2523,7 +2641,12 @@
           <t>127 – 128</t>
         </is>
       </c>
-      <c r="H65" s="4" t="inlineStr"/>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh nhận biết của bài vần ot, ôt, ơt và ảnh thật vài sự vật có tiếng chứa ba vần; HS gọi tên
+Năng lực số Miền 3 (Cơ bản, bậc 1): GV viết mẫu vần ot, ôt, ơt trên bảng tương tác theo từng nét, tô lại dấu mũ và dấu móc mà HS hay quên</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
@@ -2624,7 +2747,8 @@
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 1): Mở bài tập tương tác nối tiếng có vần et, êt, it.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh nhận biết của bài vần et, êt, it và hỏi tranh vẽ ai, đang làm gì
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở bài tập tương tác nối tiếng có vần et, êt, it với hình tương ứng; máy báo đúng, sai ngay nên HS tự nhận ra mình còn nhầm vần nào</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2780,12 @@
           <t>135 – 136</t>
         </is>
       </c>
-      <c r="H69" s="4" t="inlineStr"/>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh nhận biết của bài vần ut, ưt cùng ảnh thật vài sự vật có tiếng chứa hai vần này; ảnh lớn giúp HS gọi tên sự vật
+Năng lực số Miền 2 (Cơ bản, bậc 1): GV ghi âm lượt đọc từ ngữ của vài HS rồi mở lại cho cả lớp nghe; các em nghe giọng mình</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
@@ -2686,7 +2815,12 @@
           <t>137 – 138</t>
         </is>
       </c>
-      <c r="H70" s="4" t="inlineStr"/>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh nhận biết của bài vần ap, ăp, âp, chỉ vào từng chi tiết để HS kể việc nhân vật đang làm
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở bài tập tương tác chọn vần đúng điền vào chỗ trống giữa ap, ăp và âp; máy báo đúng, sai ngay nên HS nhận ra ba vần chỉ khác nhau ở dấu</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -2716,7 +2850,12 @@
           <t>139 – 140</t>
         </is>
       </c>
-      <c r="H71" s="4" t="inlineStr"/>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh nhận biết của bài vần op, ôp, ơp và ảnh thật vài sự vật có tiếng chứa ba vần; HS gọi tên
+Năng lực số Miền 3 (Cơ bản, bậc 1): GV viết mẫu vần op, ôp, ơp trên bảng tương tác theo từng nét, tô lại dấu mũ và dấu móc mà HS hay quên</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
@@ -2816,7 +2955,8 @@
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Chiếu phóng to tranh nhận biết của bài vần ep, êp, ip, up và hỏi tranh vẽ ai, đang làm gì.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh nhận biết của bài vần ep, êp, ip, up và hỏi tranh vẽ ai, đang làm gì
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở bài tập tương tác nối tiếng có bốn vần vừa học với hình tương ứng; máy báo đúng, sai ngay nên HS tự nhận ra mình còn nhầm vần nào</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2988,12 @@
           <t>147 – 148</t>
         </is>
       </c>
-      <c r="H75" s="4" t="inlineStr"/>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh nhận biết của bài vần anh, ênh, inh cùng ảnh thật vài sự vật có tiếng chứa ba vần này; ảnh lớn giúp HS gọi tên sự vật
+Năng lực số Miền 2 (Cơ bản, bậc 1): GV ghi âm lượt đọc từ ngữ của vài HS rồi mở lại cho cả lớp nghe; các em nghe giọng mình</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
@@ -2878,7 +3023,12 @@
           <t>149 – 150</t>
         </is>
       </c>
-      <c r="H76" s="4" t="inlineStr"/>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh nhận biết của bài vần ach, êch, ich, chỉ vào từng chi tiết để HS kể việc nhân vật đang làm
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở bài tập tương tác chọn vần đúng điền vào chỗ trống giữa ach, êch và ich; máy báo đúng</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
@@ -2908,7 +3058,12 @@
           <t>151 – 152</t>
         </is>
       </c>
-      <c r="H77" s="4" t="inlineStr"/>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh nhận biết của bài vần ang, ăng, âng và ảnh thật vài sự vật có tiếng chứa ba vần; HS gọi tên
+Năng lực số Miền 3 (Cơ bản, bậc 1): GV viết mẫu vần ang, ăng, âng trên bảng tương tác theo từng nét, tô lại dấu á và dấu mũ mà HS hay quên</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
@@ -3100,7 +3255,12 @@
           <t>163 – 164</t>
         </is>
       </c>
-      <c r="H83" s="4" t="inlineStr"/>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh nhận biết của bài vần iêt, iêu, yêu và ảnh thật vài sự vật có tiếng chứa ba vần; HS gọi tên
+Năng lực số Miền 3 (Cơ bản, bậc 1): GV viết mẫu vần iêt, iêu, yêu trên bảng tương tác theo từng nét, tô lại dấu mũ của chữ ê mà HS hay quên</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
@@ -3232,7 +3392,12 @@
           <t>171 – 172</t>
         </is>
       </c>
-      <c r="H87" s="4" t="inlineStr"/>
+      <c r="H87" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Nhận biết bài “uôc, uôt”, GV chiếu phóng to tranh mẹ chải tóc cho Hà cùng câu “Mẹ vuốt tóc và buộc nơ cho Hà.”
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở hoạt động Luyện tập đọc tiếng, GV mở bài tập tương tác: máy hiện lần lượt các tiếng có vần uôc, uôt lẫn với vần đã học</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
@@ -3262,7 +3427,12 @@
           <t>173 – 174</t>
         </is>
       </c>
-      <c r="H88" s="4" t="inlineStr"/>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Nhận biết bài “uôn, uông”, GV chiếu tranh chuồn chuồn bay trên cánh đồng lúa kèm câu “Chuồn chuồn bay qua cánh đồng lúa.” và mở một đoạn phim ngắn quay…
+Năng lực số Miền 3 (Cơ bản, bậc 1): Ở hoạt động Nói theo tranh, GV dùng điện thoại ghi âm lời từng nhóm nói về bức tranh cánh đồng</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
@@ -3292,7 +3462,12 @@
           <t>175 – 176</t>
         </is>
       </c>
-      <c r="H89" s="4" t="inlineStr"/>
+      <c r="H89" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Nhận biết bài “ươi, ươu”, GV chiếu tranh vườn cây có chim khướu cùng câu “Chim khướu hót ríu rít giữa vườn cây.” và mở đoạn âm thanh tiếng chim hót.
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở hoạt động Đọc từ ngữ, GV mở bài tập tương tác ghép vần: máy hiện các chữ cái rời, HS kéo để ghép thành vần ươi, ươu và tiếng “quả bưởi”, “hươu sao”</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
@@ -3392,7 +3567,8 @@
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>NLS-ST (Cơ bản 1): Ở hoạt động Viết, GV dùng phần mềm viết chữ chiếu nét bút chạy chậm theo đúng thứ tự của vần ươc.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Nhận biết bài “ươc, ươt”, GV chiếu phóng to tranh bạn Hà lướt sóng cùng câu nhận biết
+Năng lực số Miền 3 (Cơ bản, bậc 1): Ở hoạt động Viết, GV dùng phần mềm viết chữ chiếu nét bút chạy chậm theo đúng thứ tự của vần ươc, ươt và tiếng “lướt ván”</t>
         </is>
       </c>
     </row>
@@ -3424,7 +3600,12 @@
           <t>183 – 184</t>
         </is>
       </c>
-      <c r="H93" s="4" t="inlineStr"/>
+      <c r="H93" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Nhận biết bài “ươm, ươp”, GV chiếu tranh giàn mướp vàng có cánh bướm đậu, phóng to chỗ giàn mướp và con bướm để HS gọi tên sự vật rồi tìm…
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở hoạt động Đọc từ ngữ, GV mở bài tập tương tác ghép vần: máy hiện các chữ cái rời, HS kéo ghép thành vần ươm, ươp và tiếng “giàn mướp”, “bướm vàng”</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
@@ -3454,7 +3635,12 @@
           <t>185 – 186</t>
         </is>
       </c>
-      <c r="H94" s="4" t="inlineStr"/>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Nhận biết bài “ươn, ương”, GV chiếu tranh con đường đến trường phóng to cùng câu nhận biết, hiện dần từng cụm từ và tô sáng tiếng chứa vần mới
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở hoạt động Luyện tập đọc tiếng, GV mở bài tập tương tác: máy hiện lẫn lộn các tiếng có vần ươn, ương với vần đã học</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
@@ -3484,7 +3670,12 @@
           <t>187 – 188</t>
         </is>
       </c>
-      <c r="H95" s="4" t="inlineStr"/>
+      <c r="H95" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Nhận biết bài “oa, oe”, GV chiếu tranh khu vườn nhiều loài hoa, phóng to từng bông hoa để HS gọi tên rồi đọc câu nhận biết hiện trên màn hình…
+Năng lực số Miền 3 (Cơ bản, bậc 1): Ở hoạt động Nói theo tranh, GV dùng điện thoại ghi âm lời từng nhóm nói về khu vườn hoa rồi mở lại cho cả lớp nghe</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
@@ -3584,7 +3775,8 @@
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Ở hoạt động Nhận biết bài “oan, oăn, oat, oăt”, GV chiếu tranh voi.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Nhận biết bài “oan, oăn, oat, oăt”, GV chiếu tranh voi và thỏ phóng to cùng câu nhận biết
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở hoạt động Đọc tiếng, GV mở bài tập tương tác phân loại: máy hiện lần lượt các tiếng, HS chọn tiếng đó chứa vần oan, oăn, oat hay oăt rồi bấm kiểm tra</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3808,12 @@
           <t>195 – 196</t>
         </is>
       </c>
-      <c r="H99" s="4" t="inlineStr"/>
+      <c r="H99" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Nhận biết bài “oai, uê, uy”, GV chiếu tranh khu vườn xanh mát phóng to, chỉ vào từng sự vật để HS gọi tên rồi đọc câu nhận biết hiện dưới…
+Năng lực số Miền 3 (Cơ bản, bậc 1): Ở hoạt động Viết, GV dùng phần mềm viết chữ chiếu nét bút chạy chậm theo đúng thứ tự của vần oai, uê, uy và tiếng “khoai lang”, “hoa huệ”</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
@@ -8802,7 +8999,12 @@
           <t>75</t>
         </is>
       </c>
-      <c r="H78" s="4" t="inlineStr"/>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Khám phá bài “Phép cộng số có hai chữ số với số có một chữ số”, GV chiếu hình các bó que tính và que rời trên màn hình
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở hoạt động Luyện tập, GV mở bài tập tương tác: máy hiện phép cộng, HS chọn kết quả rồi bấm kiểm tra</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
@@ -8864,7 +9066,8 @@
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Ở hoạt động Khám phá bài “Phép cộng số có hai chữ số với số có hai chữ số”.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Khám phá bài “Phép cộng số có hai chữ số với số có hai chữ số”, GV chiếu hình các bó chục và que rời của hai số trên màn hình
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở hoạt động Luyện tập, GV mở bài tập tương tác: máy hiện phép cộng đặt tính, HS chọn kết quả rồi bấm kiểm tra</t>
         </is>
       </c>
     </row>
@@ -9014,7 +9217,8 @@
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Ở hoạt động Khám phá bài “Phép trừ số có hai chữ số cho số có hai chữ số”, GV chiếu hình.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Khám phá bài “Phép trừ số có hai chữ số cho số có hai chữ số”, GV chiếu hình các bó chục và que rời trên màn hình rồi bớt dần…
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở hoạt động Luyện tập, GV mở bài tập tương tác: máy hiện phép trừ đặt tính, HS chọn kết quả rồi bấm kiểm tra</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10507,8 @@
       <c r="H17" s="4" t="inlineStr">
         <is>
           <t>Lồng ghép GDĐP - GDQP an ninh
-NLS-KT (Cơ bản 1): Ở bài “Giữ trật tự trong trường, lớp”, GV chiếu clip ngắn cảnh xếp hàng vào lớp ngay ngắn.
+Năng lực số Miền 1 (Cơ bản, bậc 1): Ở bài “Giữ trật tự trong trường, lớp”, GV chiếu clip ngắn cảnh xếp hàng vào lớp ngay ngắn và cảnh chen lấn xô đẩy do thầy cô dựng lại
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV chiếu các tình huống trong lớp như bạn nói chuyện riêng, bạn chạy trong hành lang; HS chọn cách ứng xử phù hợp, máy báo đúng
 QPAN: Giáo dục ý thức chấp hành nội quy, pháp luật — nền nếp đầu tiên của người công dân giữ gìn an ninh, trật tự.</t>
         </is>
       </c>
@@ -18425,7 +18630,9 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN lập kế hoạch và quản lí chi tiêu, thời gian ở mức đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở phần sinh hoạt theo chủ đề của tiết “SINH HOẠT SAO: SƠ KẾT TUẦN 2 - PHƯƠNG HƯỚNG TUẦN 3”, GV chiếu ảnh chụp giờ học
+Năng lực số Miền 2 (Cơ bản, bậc 1): Ở phần khởi động và đánh giá, GV mở nhạc bài hát Em yêu trường em trên máy để cả lớp hát, vận động
+KNS: KN lập kế hoạch và quản lí chi tiêu, thời gian ở mức đơn giản.</t>
         </is>
       </c>
     </row>
@@ -19019,7 +19226,7 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>NLS-GT (Cơ bản 1): Trong giờ Sinh hoạt Sao sơ kết tuần 8, GV chiếu bảng theo dõi của lớp.
+          <t>Năng lực số Miền 2 (Cơ bản, bậc 1): Trong giờ Sinh hoạt Sao sơ kết tuần 8, GV chiếu bảng theo dõi của lớp và gõ nhận xét của từng sao ngay vào đúng dòng
 KNS: KN lập kế hoạch và quản lí chi tiêu, thời gian ở mức đơn giản.</t>
         </is>
       </c>
@@ -19427,7 +19634,7 @@
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>NLS-GT (Cơ bản 1): Trong giờ Sinh hoạt Sao sơ kết tuần 12, GV chiếu bảng theo dõi của lớp.
+          <t>Năng lực số Miền 2 (Cơ bản, bậc 1): Trong giờ Sinh hoạt Sao sơ kết tuần 12, GV chiếu bảng theo dõi của lớp và gõ nhận xét của từng sao ngay vào đúng dòng
 KNS: KN lập kế hoạch và quản lí chi tiêu, thời gian ở mức đơn giản.</t>
         </is>
       </c>
@@ -19627,7 +19834,7 @@
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>NLS-GT (Cơ bản 1): Trong giờ Sinh hoạt Sao sơ kết tuần 14, GV chiếu bảng theo dõi của lớp.</t>
+          <t>Năng lực số Miền 2 (Cơ bản, bậc 1): Trong giờ Sinh hoạt Sao sơ kết tuần 14, GV chiếu bảng theo dõi của lớp và gõ nhận xét của từng sao ngay vào đúng dòng</t>
         </is>
       </c>
     </row>
@@ -19823,7 +20030,12 @@
           <t>48</t>
         </is>
       </c>
-      <c r="H51" s="4" t="inlineStr"/>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở phần Sơ kết tuần 16, GV chiếu bảng theo dõi thi đua của lớp lên màn hình với các cột đi học đúng giờ, trực nhật, giữ vở sạch
+Năng lực số Miền 2 (Cơ bản, bậc 1): Ở phần Phương hướng tuần 17, GV mở bảng chung còn trống trên màn hình, đại diện các tổ lần lượt lên ghi việc tổ mình nhận làm</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
@@ -20015,7 +20227,12 @@
           <t>54</t>
         </is>
       </c>
-      <c r="H57" s="4" t="inlineStr"/>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở phần Sơ kết tuần 18, GV chiếu bảng theo dõi thi đua của lớp lên màn hình với các cột đi học đúng giờ, trực nhật, giữ vở sạch
+Năng lực số Miền 2 (Cơ bản, bậc 1): Ở phần Phương hướng tuần 19, GV chiếu bộ ảnh bữa ăn hợp vệ sinh và thức ăn để hở ngoài đường gắn với nội dung an toàn thực phẩm</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -20207,7 +20424,12 @@
           <t>60</t>
         </is>
       </c>
-      <c r="H63" s="4" t="inlineStr"/>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở phần Sơ kết tuần 20, GV chiếu bảng theo dõi thi đua của lớp lên màn hình với các cột đi học đúng giờ, trực nhật, giữ vở sạch, giúp bạn
+Năng lực số Miền 2 (Cơ bản, bậc 1): Ở phần Phương hướng tuần 21, GV mở bảng chung còn trống trên màn hình, đại diện các tổ lần lượt lên ghi việc tổ mình nhận làm</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -20401,7 +20623,8 @@
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Ở phần Sơ kết tuần 22, GV chiếu bảng theo dõi thi đua của lớp lên màn hình.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở phần Sơ kết tuần 22, GV chiếu bảng theo dõi thi đua của lớp lên màn hình với các cột đi học đúng giờ, trực nhật, giữ vở sạch, giúp bạn
+Năng lực số Miền 2 (Cơ bản, bậc 1): Ở phần Phương hướng tuần 23, GV mở bảng chung còn trống trên màn hình, đại diện các tổ lần lượt lên ghi việc tổ mình nhận làm
 KNS: KN lập kế hoạch và quản lí chi tiêu, thời gian ở mức đơn giản.</t>
         </is>
       </c>
@@ -20602,7 +20825,8 @@
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Ở phần Sơ kết tuần 24, GV chiếu bảng theo dõi thi đua của lớp lên màn hình.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở phần Sơ kết tuần 24, GV chiếu bảng theo dõi thi đua của lớp lên màn hình với các cột đi học đúng giờ, trực nhật, giữ vở sạch, giúp bạn
+Năng lực số Miền 2 (Cơ bản, bậc 1): Ở phần Phương hướng tuần 25, GV mở bảng chung còn trống trên màn hình, đại diện các tổ lần lượt lên ghi việc tổ mình nhận làm
 KNS: KN lập kế hoạch và quản lí chi tiêu, thời gian ở mức đơn giản.</t>
         </is>
       </c>
@@ -20991,7 +21215,12 @@
           <t>84</t>
         </is>
       </c>
-      <c r="H87" s="4" t="inlineStr"/>
+      <c r="H87" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở phần Sơ kết tuần 28, GV chiếu bảng theo dõi thi đua của lớp lên màn hình với các cột đi học đúng giờ, trực nhật, giữ vở sạch, giúp bạn
+Năng lực số Miền 2 (Cơ bản, bậc 1): Ở phần Phương hướng tuần 29, GV mở bảng chung còn trống trên màn hình, đại diện các tổ lần lượt lên ghi việc tổ mình nhận làm</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
@@ -21189,7 +21418,9 @@
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN lập kế hoạch và quản lí chi tiêu, thời gian ở mức đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở phần Sơ kết tuần 30, GV chiếu bảng theo dõi thi đua của lớp lên màn hình với các cột đi học đúng giờ, trực nhật, giữ vở sạch, chăm sóc cây
+Năng lực số Miền 2 (Cơ bản, bậc 1): Ở phần Phương hướng tuần 31, GV mở bảng chung còn trống trên màn hình, đại diện các tổ lần lượt lên ghi việc tổ mình nhận làm
+KNS: KN lập kế hoạch và quản lí chi tiêu, thời gian ở mức đơn giản.</t>
         </is>
       </c>
     </row>

--- a/assets/docs/lop1/KHDH ca khoi - Lop 1.xlsx
+++ b/assets/docs/lop1/KHDH ca khoi - Lop 1.xlsx
@@ -944,7 +944,12 @@
           <t>27 – 28</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh nhận biết “Bố và Hà đi bộ trên hè phố” của bài chữ ô và thanh nặng
+Năng lực số Miền 2 (Cơ bản, bậc 1): GV ghi âm lượt đọc từ bố, cô bé, cổ cò của vài HS rồi mở lại cho cả lớp cùng nghe; các em nghe giọng mình</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -1009,7 +1014,12 @@
           <t>31 – 32</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr"/>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh nhận biết “Tàu dỡ hàng ở cảng” của bài chữ ơ và dấu ngã, thêm vài ảnh thật về bờ đê, con cá cờ
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở bài tập tương tác chọn tiếng viết đúng dấu ngã trong các cặp tiếng dễ lẫn như dỡ và dở, đỡ và đở; máy báo đúng</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -1419,7 +1429,12 @@
           <t>55 – 56</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr"/>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh nhận biết của bài chữ ng, ngh và ảnh thật vài sự vật có tiếng chứa hai chữ ghép này; HS gọi tên, tìm tiếng có ng
+Năng lực số Miền 3 (Cơ bản, bậc 1): GV viết mẫu chữ ng, ngh trên bảng tương tác theo từng nét, tô lại chỗ nối nét mà HS hay viết rời</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -1552,7 +1567,12 @@
           <t>63 – 64</t>
         </is>
       </c>
-      <c r="H33" s="4" t="inlineStr"/>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh nhận biết của bài chữ t, tr cùng ảnh thật vài sự vật có tiếng chứa t, tr để HS gọi tên
+Năng lực số Miền 2 (Cơ bản, bậc 1): GV ghi âm lượt đọc từ ngữ của vài HS rồi mở lại cho cả lớp nghe; các em nghe giọng mình</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -1582,7 +1602,12 @@
           <t>65 – 66</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr"/>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh nhận biết của bài chữ th và vần ia, chỉ vào từng chi tiết để HS kể việc các nhân vật đang làm
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở bài tập tương tác ghép âm đầu với vần ia thành tiếng rồi nối tiếng với hình; máy báo đúng</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -2028,7 +2053,12 @@
           <t>91 – 92</t>
         </is>
       </c>
-      <c r="H47" s="4" t="inlineStr"/>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh nhận biết của bài vần am, ăm, âm và ảnh thật vài sự vật có tiếng chứa ba vần; HS gọi tên
+Năng lực số Miền 3 (Cơ bản, bậc 1): GV viết mẫu vần am, ăm, âm trên bảng tương tác theo từng nét, tô lại dấu mũ và dấu á mà HS hay quên</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
@@ -2369,7 +2399,12 @@
           <t>111 – 112</t>
         </is>
       </c>
-      <c r="H57" s="4" t="inlineStr"/>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh nhận biết của bài vần ao, eo cùng ảnh thật vài sự vật có tiếng chứa hai vần này; ảnh lớn giúp HS gọi tên sự vật
+Năng lực số Miền 2 (Cơ bản, bậc 1): GV ghi âm lượt đọc từ ngữ của vài HS rồi mở lại cho cả lớp nghe; các em nghe giọng mình</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -2539,7 +2574,8 @@
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Chiếu phóng to tranh nhận biết của bài vần ac, ăc, âc và hỏi tranh vẽ ai, đang làm gì.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh nhận biết của bài vần ac, ăc, âc và hỏi tranh vẽ ai, đang làm gì
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở bài tập tương tác nối tiếng có vần ac, ăc, âc với hình tương ứng; máy báo đúng, sai ngay nên HS tự nhận ra mình còn nhầm vần nào</t>
         </is>
       </c>
     </row>
@@ -3163,7 +3199,8 @@
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 1): Mở bài tập tương tác nối tiếng có bốn vần vừa học.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh nhận biết của bài vần ong, ông, ung, ưng và hỏi tranh vẽ ai, đang làm gì
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở bài tập tương tác nối tiếng có bốn vần vừa học với hình tương ứng; máy báo đúng, sai ngay nên HS tự nhận ra mình còn nhầm vần nào</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3232,12 @@
           <t>159 – 160</t>
         </is>
       </c>
-      <c r="H81" s="4" t="inlineStr"/>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh nhận biết của bài vần iêc, iên, iêp cùng ảnh thật vài sự vật có tiếng chứa ba vần này; ảnh lớn giúp HS gọi tên sự vật
+Năng lực số Miền 2 (Cơ bản, bậc 1): GV ghi âm lượt đọc từ ngữ của vài HS rồi mở lại cho cả lớp nghe; các em nghe giọng mình</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
@@ -3225,7 +3267,12 @@
           <t>161 – 162</t>
         </is>
       </c>
-      <c r="H82" s="4" t="inlineStr"/>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh nhận biết của bài vần iêng, iêm, yên, chỉ vào từng chi tiết để HS kể việc nhân vật đang làm
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở bài tập tương tác chọn vần đúng điền vào chỗ trống giữa iên và yên; máy báo đúng, sai ngay nên HS bước đầu nhận ra khi nào viết yên</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
@@ -3360,7 +3407,8 @@
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Ở hoạt động Nhận biết bài “uôi, uôm”, GV chiếu phóng to tranh con thuyền và câu “Thuyền buồm xuôi theo chiều gió.”.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Nhận biết bài “uôi, uôm”, GV chiếu phóng to tranh con thuyền và câu “Thuyền buồm xuôi theo chiều gió.”
+Năng lực số Miền 3 (Cơ bản, bậc 1): Ở hoạt động Viết, GV dùng phần mềm viết chữ chiếu nét bút chạy chậm theo đúng thứ tự của vần uôi, uôm và tiếng “nải chuối”</t>
         </is>
       </c>
     </row>
@@ -3843,7 +3891,12 @@
           <t>197 – 198</t>
         </is>
       </c>
-      <c r="H100" s="4" t="inlineStr"/>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Nhận biết bài “uân, uât”, GV chiếu tranh cảnh mùa xuân và mở một đoạn phim ngắn về chợ hoa ngày Tết để HS thấy không khí mùa xuân
+Năng lực số Miền 3 (Cơ bản, bậc 1): Ở hoạt động Nói theo tranh, GV ghi âm lời từng nhóm nói về cảnh mùa xuân trong tranh rồi mở lại cho cả lớp nghe</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
@@ -3873,7 +3926,12 @@
           <t>199 – 200</t>
         </is>
       </c>
-      <c r="H101" s="4" t="inlineStr"/>
+      <c r="H101" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Nhận biết bài “uyên, uyêt”, GV chiếu tranh bà kể chuyện cho cháu nghe và mở bản kể chuyện có tiếng đọc mẫu
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở hoạt động Đọc từ ngữ, GV mở bài tập tương tác ghép vần: máy hiện các chữ cái rời, HS kéo ghép thành vần uyên, uyêt và tiếng “câu chuyện”, “thuyền buồm”</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
@@ -9131,7 +9189,8 @@
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 1): Ở hoạt động Luyện tập, GV mở bài tập tương tác: máy hiện phép trừ, HS chọn kết quả rồi bấm kiểm tra.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Khám phá bài “Phép trừ số có hai chữ số cho số có một chữ số”, GV chiếu hình bó chục và que rời trên màn hình rồi bớt dần số…
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở hoạt động Luyện tập, GV mở bài tập tương tác: máy hiện phép trừ, HS chọn kết quả rồi bấm kiểm tra</t>
         </is>
       </c>
     </row>
@@ -10131,7 +10190,8 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Chiếu phóng to tranh Khám phá của bài “Em tắm, gội sạch sẽ” cho HS so sánh hai bạn trong tranh.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh Khám phá của bài “Em tắm, gội sạch sẽ” cho HS so sánh hai bạn trong tranh
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở bài tập tương tác kéo các bước tắm, gội về đúng thứ tự; máy báo đúng, sai ngay nên HS tự nhận ra chỗ xếp nhầm và sắp lại</t>
         </is>
       </c>
     </row>
@@ -10165,7 +10225,8 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 1): Mở bài tập tương tác sắp các bước mặc áo và chỉnh trang phục theo đúng thứ tự.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh Khám phá của bài “Em giữ trang phục gọn gàng, sạch sẽ” và thêm vài ảnh thật: áo bỏ trong quần, cổ áo lật ngay ngắn
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở bài tập tương tác sắp các bước mặc áo và chỉnh trang phục theo đúng thứ tự: mặc áo, cài cúc từ dưới lên, bỏ áo vào quần, chỉnh cổ áo
 KNS: KN tự phục vụ: tự làm lấy việc của mình, giữ gìn vệ sinh cá nhân và nơi ở.</t>
         </is>
       </c>
@@ -10543,7 +10604,8 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 1): Ở hoạt động Luyện tập, GV mở trên máy chiếu bài tập kéo thả.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Khám phá bài “Giữ gìn tài sản của trường, lớp”, GV chiếu lên màn hình bộ ảnh chụp ngay tại trường mình: bộ bàn ghế còn lành và bộ bàn bị…
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở hoạt động Luyện tập, GV mở trên máy chiếu bài tập kéo thả: các bức tranh việc làm hiện ra, HS lên bảng kéo tranh vào cột “Nên làm” hoặc “Không nên làm”
 KNS: KN chi tiêu và giữ gìn: dùng đồ dùng, tiền bạc hợp lí, giữ gìn của công.</t>
         </is>
       </c>
@@ -10578,7 +10640,8 @@
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Ở hoạt động Khám phá bài “Giữ vệ sinh trường, lớp”, GV chiếu ảnh chụp chính lớp mình lúc đầu buổi và.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Khám phá bài “Giữ vệ sinh trường, lớp”, GV chiếu ảnh chụp chính lớp mình lúc đầu buổi và sau khi trực nhật, phóng to góc để chổi
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở hoạt động Luyện tập, GV mở bài tập tương tác phân loại rác trên máy chiếu: máy hiện lần lượt vỏ hộp sữa, giấy vụn, lá cây
 KNS: KN tự phục vụ: tự làm lấy việc của mình, giữ gìn vệ sinh cá nhân và nơi ở.</t>
         </is>
       </c>
@@ -10613,7 +10676,8 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 1): Ở hoạt động Luyện tập, GV mở bài tập tương tác sắp xếp đồ dùng.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Khám phá bài “Gọn gàng, ngăn nắp”, GV chiếu hai ảnh chụp cùng một góc học tập: lúc sách vở để lộn xộn và lúc đã xếp gọn
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở hoạt động Luyện tập, GV mở bài tập tương tác sắp xếp đồ dùng: máy hiện bàn học bừa bộn, HS kéo từng thứ về đúng chỗ là giá sách, hộp bút
 KNS: KN tự phục vụ: tự làm lấy việc của mình, giữ gìn vệ sinh cá nhân và nơi ở.</t>
         </is>
       </c>
@@ -10752,7 +10816,8 @@
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Ở hoạt động Khám phá bài “Tự giác tham gia các hoạt động ở trường”, GV chiếu ảnh chụp chính các hoạt động của trường mình.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Khám phá bài “Tự giác tham gia các hoạt động ở trường”, GV chiếu ảnh chụp chính các hoạt động của trường mình: kế hoạch nhỏ, chăm sóc bồn hoa
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở hoạt động Luyện tập, GV mở bài tập tương tác: máy hiện các việc chung ở trường, HS chọn việc vừa sức mình có thể tự giác làm rồi bấm kiểm tra
 KNS: KN tự phục vụ: tự làm lấy việc của mình, giữ gìn vệ sinh cá nhân và nơi ở.</t>
         </is>
       </c>
@@ -10787,7 +10852,8 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 1): Ở hoạt động Luyện tập, GV mở bài tập tương tác phân loại.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Khám phá bài “Tự giác làm việc nhà”, GV chiếu bộ ảnh những việc nhà vừa sức với HS lớp 1: gấp quần áo, tưới cây, nhặt rau, xếp dép
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở hoạt động Luyện tập, GV mở bài tập tương tác phân loại: máy hiện lần lượt các việc nhà, HS chọn việc vừa sức và an toàn hay việc phải nhờ người lớn…
 KNS: KN tự phục vụ: tự làm lấy việc của mình, giữ gìn vệ sinh cá nhân và nơi ở.</t>
         </is>
       </c>
@@ -11161,7 +11227,8 @@
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 1): Nêu và làm mẫu cách người lớn quét mã trên bao bì để tra thông tin sản phẩm.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu ảnh phóng to nhãn một gói bánh, hộp sữa lên màn hình, chỉ cho HS chỗ ghi hạn sử dụng và hướng dẫn HS đọc số ngày tháng ghi ở đó.
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV nêu và làm mẫu cách người lớn quét mã trên bao bì để tra thông tin sản phẩm; HS quan sát GV thao tác và nói lại việc cần làm trước khi ăn…</t>
         </is>
       </c>
     </row>
@@ -19026,7 +19093,8 @@
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN lập kế hoạch và quản lí chi tiêu, thời gian ở mức đơn giản.</t>
+          <t>Năng lực số Miền 2 (Cơ bản, bậc 1): Trong giờ Sinh hoạt Sao sơ kết tuần 6, GV chiếu bảng theo dõi của lớp lên màn hình và gõ ngay nhận xét của từng sao vào đúng dòng
+KNS: KN lập kế hoạch và quản lí chi tiêu, thời gian ở mức đơn giản.</t>
         </is>
       </c>
     </row>
@@ -19433,7 +19501,8 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN lập kế hoạch và quản lí chi tiêu, thời gian ở mức đơn giản.</t>
+          <t>Năng lực số Miền 2 (Cơ bản, bậc 1): Trong giờ Sinh hoạt Sao sơ kết tuần 10, GV chiếu bảng theo dõi của lớp và gõ nhận xét của từng sao ngay vào đúng dòng
+KNS: KN lập kế hoạch và quản lí chi tiêu, thời gian ở mức đơn giản.</t>
         </is>
       </c>
     </row>
@@ -21627,7 +21696,8 @@
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>NLS-GT (Cơ bản 1): Ở phần Phương hướng tuần 33, GV mở bảng chung còn trống trên màn hình, đại diện các tổ lần lượt lên.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở phần Sơ kết tuần 32, GV chiếu bảng theo dõi thi đua cả năm của lớp lên màn hình, tô màu những tuần lớp làm tốt để HS nhìn thấy sự tiến bộ…
+Năng lực số Miền 2 (Cơ bản, bậc 1): Ở phần Phương hướng tuần 33, GV mở bảng chung còn trống trên màn hình, đại diện các tổ lần lượt lên ghi việc tổ mình nhận làm
 KNS: KN lập kế hoạch và quản lí chi tiêu, thời gian ở mức đơn giản.</t>
         </is>
       </c>
@@ -21833,7 +21903,8 @@
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t>NLS-GT (Cơ bản 1): Ở phần Phương hướng tuần 35, GV mở bảng chung còn trống trên màn hình, đại diện các tổ lần lượt lên.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở phần Sơ kết tuần 34, GV chiếu bảng theo dõi thi đua cả năm của lớp lên màn hình, tô màu những việc lớp đã làm tốt để HS nhìn lại một năm…
+Năng lực số Miền 2 (Cơ bản, bậc 1): Ở phần Phương hướng tuần 35, GV mở bảng chung còn trống trên màn hình, đại diện các tổ lần lượt lên ghi việc tổ mình nhận làm trong tuần cuối năm
 KNS: KN lập kế hoạch và quản lí chi tiêu, thời gian ở mức đơn giản.</t>
         </is>
       </c>

--- a/assets/docs/lop1/KHDH ca khoi - Lop 1.xlsx
+++ b/assets/docs/lop1/KHDH ca khoi - Lop 1.xlsx
@@ -16099,7 +16099,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>3 tiết</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -16134,7 +16134,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>3 tiết</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -16168,7 +16168,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>3 tiết</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
@@ -16202,7 +16202,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>4 tiết</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -16237,7 +16237,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>4 tiết</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -16271,7 +16271,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>4 tiết</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -16306,7 +16306,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>4 tiết</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -16340,7 +16340,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>4 tiết</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -16375,7 +16375,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>4 tiết</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -16409,7 +16409,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>4 tiết</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
@@ -16444,7 +16444,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>4 tiết</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -16478,7 +16478,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>3 tiết</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>3 tiết</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -16547,7 +16547,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>3 tiết</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -16581,7 +16581,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>2 tiết</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -16615,7 +16615,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>2 tiết</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
@@ -16645,7 +16645,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>3 tiết</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
@@ -16679,7 +16679,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>3 tiết</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
@@ -16709,7 +16709,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>3 tiết</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
@@ -16743,7 +16743,7 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>2 tiết</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
@@ -16777,7 +16777,7 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>2 tiết</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
@@ -16841,7 +16841,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>3 tiết</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
@@ -16876,7 +16876,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>3 tiết</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
@@ -16910,7 +16910,7 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>3 tiết</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
@@ -16944,7 +16944,7 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>4 tiết</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
@@ -16979,7 +16979,7 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>4 tiết</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
@@ -17013,7 +17013,7 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>4 tiết</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
@@ -17048,7 +17048,7 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>4 tiết</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
@@ -17082,7 +17082,7 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>5 tiết</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
@@ -17117,7 +17117,7 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>5 tiết</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
@@ -17151,7 +17151,7 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>5 tiết</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
@@ -17186,7 +17186,7 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>5 tiết</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
@@ -17220,7 +17220,7 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>5 tiết</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
@@ -17318,7 +17318,7 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>6 tiết</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
@@ -17353,7 +17353,7 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>6 tiết</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
@@ -17387,7 +17387,7 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>6 tiết</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
@@ -17422,7 +17422,7 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>6 tiết</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
@@ -17456,7 +17456,7 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>6 tiết</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
@@ -17491,7 +17491,7 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>6 tiết</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
@@ -17525,7 +17525,7 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>6 tiết</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
@@ -17560,7 +17560,7 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>6 tiết</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
@@ -17594,7 +17594,7 @@
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>6 tiết</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>6 tiết</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
@@ -17663,7 +17663,7 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>6 tiết</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
@@ -17698,7 +17698,7 @@
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>6 tiết</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
@@ -17732,7 +17732,7 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>4 tiết</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
@@ -17766,7 +17766,7 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>4 tiết</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
@@ -17796,7 +17796,7 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>4 tiết</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
@@ -17826,7 +17826,7 @@
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>4 tiết</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
@@ -17860,7 +17860,7 @@
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>4 tiết</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
@@ -17894,7 +17894,7 @@
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>4 tiết</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
@@ -17924,7 +17924,7 @@
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>4 tiết</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
@@ -17954,7 +17954,7 @@
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>4 tiết</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
@@ -18022,7 +18022,7 @@
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>5 tiết</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
@@ -18056,7 +18056,7 @@
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>5 tiết</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
@@ -18086,7 +18086,7 @@
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>5 tiết</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>5 tiết</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
@@ -18150,7 +18150,7 @@
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>5 tiết</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>5 tiết</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>5 tiết</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
@@ -18244,7 +18244,7 @@
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>5 tiết</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
@@ -18274,7 +18274,7 @@
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>5 tiết</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
@@ -18308,7 +18308,7 @@
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>5 tiết</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">

--- a/assets/docs/lop1/KHDH ca khoi - Lop 1.xlsx
+++ b/assets/docs/lop1/KHDH ca khoi - Lop 1.xlsx
@@ -18896,7 +18896,8 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN lập kế hoạch và quản lí chi tiêu, thời gian ở mức đơn giản.</t>
+          <t>Năng lực số 1.1 CB1b: HS hình dung và kể lại được việc sắp làm sau khi xem ảnh, video minh hoạ.
+KNS: KN lập kế hoạch và quản lí chi tiêu, thời gian ở mức đơn giản.</t>
         </is>
       </c>
     </row>

--- a/assets/docs/lop1/KHDH ca khoi - Lop 1.xlsx
+++ b/assets/docs/lop1/KHDH ca khoi - Lop 1.xlsx
@@ -542,7 +542,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ I · LÀM QUEN</t>
+          <t>Học kì I · Làm quen</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr"/>
@@ -577,7 +577,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ I · LÀM QUEN</t>
+          <t>Học kì I · Làm quen</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr"/>
@@ -612,7 +612,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ I · LÀM QUEN</t>
+          <t>Học kì I · Làm quen</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr"/>
@@ -647,7 +647,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ I · LÀM QUEN</t>
+          <t>Học kì I · Làm quen</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr"/>
@@ -682,7 +682,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>HỌC ÂM (CHỮ CÁI)</t>
+          <t>Học âm (chữ cái)</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr"/>
@@ -716,7 +716,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>HỌC ÂM (CHỮ CÁI)</t>
+          <t>Học âm (chữ cái)</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
@@ -751,7 +751,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>HỌC ÂM (CHỮ CÁI)</t>
+          <t>Học âm (chữ cái)</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr"/>
@@ -786,7 +786,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>HỌC ÂM (CHỮ CÁI)</t>
+          <t>Học âm (chữ cái)</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr"/>
@@ -821,7 +821,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>HỌC ÂM (CHỮ CÁI)</t>
+          <t>Học âm (chữ cái)</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr"/>
@@ -855,7 +855,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>HỌC ÂM (CHỮ CÁI)</t>
+          <t>Học âm (chữ cái)</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr"/>
@@ -889,7 +889,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>HỌC ÂM (CHỮ CÁI)</t>
+          <t>Học âm (chữ cái)</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr"/>
@@ -924,7 +924,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>HỌC ÂM (CHỮ CÁI)</t>
+          <t>Học âm (chữ cái)</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr"/>
@@ -959,7 +959,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>HỌC ÂM (CHỮ CÁI)</t>
+          <t>Học âm (chữ cái)</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr"/>
@@ -994,7 +994,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>HỌC ÂM (CHỮ CÁI)</t>
+          <t>Học âm (chữ cái)</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr"/>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>HỌC ÂM (CHỮ CÁI)</t>
+          <t>Học âm (chữ cái)</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr"/>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>HỌC ÂM (CHỮ CÁI)</t>
+          <t>Học âm (chữ cái)</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr"/>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>HỌC ÂM (CHỮ CÁI)</t>
+          <t>Học âm (chữ cái)</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr"/>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>HỌC ÂM (CHỮ CÁI)</t>
+          <t>Học âm (chữ cái)</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr"/>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>HỌC ÂM (CHỮ CÁI)</t>
+          <t>Học âm (chữ cái)</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr"/>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>HỌC ÂM (CHỮ CÁI)</t>
+          <t>Học âm (chữ cái)</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr"/>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>HỌC ÂM (CHỮ CÁI)</t>
+          <t>Học âm (chữ cái)</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr"/>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>HỌC ÂM (CHỮ CÁI)</t>
+          <t>Học âm (chữ cái)</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr"/>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>HỌC ÂM (CHỮ CÁI)</t>
+          <t>Học âm (chữ cái)</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr"/>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>HỌC ÂM (CHỮ CÁI)</t>
+          <t>Học âm (chữ cái)</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr"/>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>HỌC ÂM (CHỮ CÁI)</t>
+          <t>Học âm (chữ cái)</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr"/>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>HỌC ÂM (CHỮ CÁI)</t>
+          <t>Học âm (chữ cái)</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr"/>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>HỌC ÂM (CHỮ CÁI)</t>
+          <t>Học âm (chữ cái)</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr"/>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>HỌC ÂM (CHỮ CÁI)</t>
+          <t>Học âm (chữ cái)</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr"/>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>HỌC ÂM (CHỮ CÁI)</t>
+          <t>Học âm (chữ cái)</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr"/>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>HỌC ÂM (CHỮ CÁI)</t>
+          <t>Học âm (chữ cái)</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr"/>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>HỌC ÂM (CHỮ CÁI)</t>
+          <t>Học âm (chữ cái)</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr"/>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>HỌC ÂM (CHỮ CÁI)</t>
+          <t>Học âm (chữ cái)</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr"/>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>HỌC ÂM (CHỮ CÁI)</t>
+          <t>Học âm (chữ cái)</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr"/>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>HỌC ÂM (CHỮ CÁI)</t>
+          <t>Học âm (chữ cái)</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr"/>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>HỌC ÂM (CHỮ CÁI)</t>
+          <t>Học âm (chữ cái)</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr"/>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>HỌC ÂM (CHỮ CÁI)</t>
+          <t>Học âm (chữ cái)</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr"/>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>HỌC ÂM (CHỮ CÁI)</t>
+          <t>Học âm (chữ cái)</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr"/>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>HỌC ÂM (CHỮ CÁI)</t>
+          <t>Học âm (chữ cái)</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr"/>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>HỌC ÂM (CHỮ CÁI)</t>
+          <t>Học âm (chữ cái)</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr"/>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>HỌC ÂM (CHỮ CÁI)</t>
+          <t>Học âm (chữ cái)</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr"/>
@@ -1928,7 +1928,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr"/>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr"/>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr"/>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr"/>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr"/>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr"/>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr"/>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr"/>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr"/>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr"/>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr"/>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr"/>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr"/>
@@ -2379,7 +2379,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr"/>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr"/>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr"/>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr"/>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr"/>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr"/>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr"/>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr"/>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr"/>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr"/>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr"/>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr"/>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr"/>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr"/>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr"/>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr"/>
@@ -2935,7 +2935,7 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr"/>
@@ -2969,7 +2969,7 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr"/>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr"/>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr"/>
@@ -3074,7 +3074,7 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr"/>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr"/>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr"/>
@@ -3177,7 +3177,7 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr"/>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr"/>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr"/>
@@ -3282,7 +3282,7 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr"/>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr"/>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr"/>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr"/>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr"/>
@@ -3455,7 +3455,7 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr"/>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr"/>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr"/>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr"/>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr"/>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr"/>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr"/>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr"/>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr"/>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr"/>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr"/>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr"/>
@@ -3871,7 +3871,7 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr"/>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr"/>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr"/>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>HỌC VẦN</t>
+          <t>Học vần</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr"/>
@@ -4009,7 +4009,7 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>ÔN TẬP CUỐI HỌC KÌ I</t>
+          <t>Ôn tập cuối học kì I</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr"/>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>ÔN TẬP CUỐI HỌC KÌ I</t>
+          <t>Ôn tập cuối học kì I</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr"/>
@@ -4077,7 +4077,7 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>ÔN TẬP CUỐI HỌC KÌ I</t>
+          <t>Ôn tập cuối học kì I</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr"/>
@@ -4111,7 +4111,7 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>ÔN TẬP CUỐI HỌC KÌ I</t>
+          <t>Ôn tập cuối học kì I</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr"/>
@@ -4141,7 +4141,7 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 1: TÔI VÀ CÁC BẠN</t>
+          <t>Học kì II · Chủ điểm 1: Tôi và các bạn</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr"/>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 1: TÔI VÀ CÁC BẠN</t>
+          <t>Học kì II · Chủ điểm 1: Tôi và các bạn</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr"/>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 1: TÔI VÀ CÁC BẠN</t>
+          <t>Học kì II · Chủ điểm 1: Tôi và các bạn</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr"/>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 1: TÔI VÀ CÁC BẠN</t>
+          <t>Học kì II · Chủ điểm 1: Tôi và các bạn</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr"/>
@@ -4278,7 +4278,7 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 1: TÔI VÀ CÁC BẠN</t>
+          <t>Học kì II · Chủ điểm 1: Tôi và các bạn</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr"/>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 1: TÔI VÀ CÁC BẠN</t>
+          <t>Học kì II · Chủ điểm 1: Tôi và các bạn</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr"/>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 1: TÔI VÀ CÁC BẠN</t>
+          <t>Học kì II · Chủ điểm 1: Tôi và các bạn</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr"/>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 1: TÔI VÀ CÁC BẠN</t>
+          <t>Học kì II · Chủ điểm 1: Tôi và các bạn</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr"/>
@@ -4415,7 +4415,7 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 2: MÁI ẤM GIA ĐÌNH</t>
+          <t>Học kì II · Chủ điểm 2: Mái ấm gia đình</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr"/>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 2: MÁI ẤM GIA ĐÌNH</t>
+          <t>Học kì II · Chủ điểm 2: Mái ấm gia đình</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr"/>
@@ -4484,7 +4484,7 @@
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 2: MÁI ẤM GIA ĐÌNH</t>
+          <t>Học kì II · Chủ điểm 2: Mái ấm gia đình</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr"/>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 2: MÁI ẤM GIA ĐÌNH</t>
+          <t>Học kì II · Chủ điểm 2: Mái ấm gia đình</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr"/>
@@ -4553,7 +4553,7 @@
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 2: MÁI ẤM GIA ĐÌNH</t>
+          <t>Học kì II · Chủ điểm 2: Mái ấm gia đình</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr"/>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 2: MÁI ẤM GIA ĐÌNH</t>
+          <t>Học kì II · Chủ điểm 2: Mái ấm gia đình</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr"/>
@@ -4623,7 +4623,7 @@
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 2: MÁI ẤM GIA ĐÌNH</t>
+          <t>Học kì II · Chủ điểm 2: Mái ấm gia đình</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr"/>
@@ -4657,7 +4657,7 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 2: MÁI ẤM GIA ĐÌNH</t>
+          <t>Học kì II · Chủ điểm 2: Mái ấm gia đình</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr"/>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 2: MÁI ẤM GIA ĐÌNH</t>
+          <t>Học kì II · Chủ điểm 2: Mái ấm gia đình</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr"/>
@@ -4725,7 +4725,7 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 3: MÁI TRƯỜNG MẾN YÊU</t>
+          <t>Học kì II · Chủ điểm 3: Mái trường mến yêu</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr"/>
@@ -4760,7 +4760,7 @@
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 3: MÁI TRƯỜNG MẾN YÊU</t>
+          <t>Học kì II · Chủ điểm 3: Mái trường mến yêu</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr"/>
@@ -4795,7 +4795,7 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 3: MÁI TRƯỜNG MẾN YÊU</t>
+          <t>Học kì II · Chủ điểm 3: Mái trường mến yêu</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr"/>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 3: MÁI TRƯỜNG MẾN YÊU</t>
+          <t>Học kì II · Chủ điểm 3: Mái trường mến yêu</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr"/>
@@ -4863,7 +4863,7 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 3: MÁI TRƯỜNG MẾN YÊU</t>
+          <t>Học kì II · Chủ điểm 3: Mái trường mến yêu</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr"/>
@@ -4897,7 +4897,7 @@
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 3: MÁI TRƯỜNG MẾN YÊU</t>
+          <t>Học kì II · Chủ điểm 3: Mái trường mến yêu</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr"/>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 3: MÁI TRƯỜNG MẾN YÊU</t>
+          <t>Học kì II · Chủ điểm 3: Mái trường mến yêu</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr"/>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 3: MÁI TRƯỜNG MẾN YÊU</t>
+          <t>Học kì II · Chủ điểm 3: Mái trường mến yêu</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr"/>
@@ -4999,7 +4999,7 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 3: MÁI TRƯỜNG MẾN YÊU</t>
+          <t>Học kì II · Chủ điểm 3: Mái trường mến yêu</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr"/>
@@ -5033,7 +5033,7 @@
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 4: ĐIỀU EM CẦN BIẾT</t>
+          <t>Học kì II · Chủ điểm 4: Điều em cần biết</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr"/>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 4: ĐIỀU EM CẦN BIẾT</t>
+          <t>Học kì II · Chủ điểm 4: Điều em cần biết</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr"/>
@@ -5101,7 +5101,7 @@
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 4: ĐIỀU EM CẦN BIẾT</t>
+          <t>Học kì II · Chủ điểm 4: Điều em cần biết</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr"/>
@@ -5136,7 +5136,7 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 4: ĐIỀU EM CẦN BIẾT</t>
+          <t>Học kì II · Chủ điểm 4: Điều em cần biết</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr"/>
@@ -5170,7 +5170,7 @@
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 4: ĐIỀU EM CẦN BIẾT</t>
+          <t>Học kì II · Chủ điểm 4: Điều em cần biết</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr"/>
@@ -5204,7 +5204,7 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 4: ĐIỀU EM CẦN BIẾT</t>
+          <t>Học kì II · Chủ điểm 4: Điều em cần biết</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr"/>
@@ -5240,7 +5240,7 @@
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 4: ĐIỀU EM CẦN BIẾT</t>
+          <t>Học kì II · Chủ điểm 4: Điều em cần biết</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr"/>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 4: ĐIỀU EM CẦN BIẾT</t>
+          <t>Học kì II · Chủ điểm 4: Điều em cần biết</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr"/>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 5: BÀI HỌC TỪ CUỘC SỐNG</t>
+          <t>Học kì II · Chủ điểm 5: Bài học từ cuộc sống</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr"/>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 5: BÀI HỌC TỪ CUỘC SỐNG</t>
+          <t>Học kì II · Chủ điểm 5: Bài học từ cuộc sống</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr"/>
@@ -5377,7 +5377,7 @@
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 5: BÀI HỌC TỪ CUỘC SỐNG</t>
+          <t>Học kì II · Chủ điểm 5: Bài học từ cuộc sống</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr"/>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 5: BÀI HỌC TỪ CUỘC SỐNG</t>
+          <t>Học kì II · Chủ điểm 5: Bài học từ cuộc sống</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr"/>
@@ -5445,7 +5445,7 @@
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 5: BÀI HỌC TỪ CUỘC SỐNG</t>
+          <t>Học kì II · Chủ điểm 5: Bài học từ cuộc sống</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr"/>
@@ -5480,7 +5480,7 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 5: BÀI HỌC TỪ CUỘC SỐNG</t>
+          <t>Học kì II · Chủ điểm 5: Bài học từ cuộc sống</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr"/>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 5: BÀI HỌC TỪ CUỘC SỐNG</t>
+          <t>Học kì II · Chủ điểm 5: Bài học từ cuộc sống</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr"/>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 5: BÀI HỌC TỪ CUỘC SỐNG</t>
+          <t>Học kì II · Chủ điểm 5: Bài học từ cuộc sống</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr"/>
@@ -5582,7 +5582,7 @@
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 6: THIÊN NHIÊN KÌ THÚ</t>
+          <t>Học kì II · Chủ điểm 6: Thiên nhiên kì thú</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr"/>
@@ -5617,7 +5617,7 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 6: THIÊN NHIÊN KÌ THÚ</t>
+          <t>Học kì II · Chủ điểm 6: Thiên nhiên kì thú</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr"/>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 6: THIÊN NHIÊN KÌ THÚ</t>
+          <t>Học kì II · Chủ điểm 6: Thiên nhiên kì thú</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr"/>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 6: THIÊN NHIÊN KÌ THÚ</t>
+          <t>Học kì II · Chủ điểm 6: Thiên nhiên kì thú</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr"/>
@@ -5720,7 +5720,7 @@
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 6: THIÊN NHIÊN KÌ THÚ</t>
+          <t>Học kì II · Chủ điểm 6: Thiên nhiên kì thú</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr"/>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 6: THIÊN NHIÊN KÌ THÚ</t>
+          <t>Học kì II · Chủ điểm 6: Thiên nhiên kì thú</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr"/>
@@ -5788,7 +5788,7 @@
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 6: THIÊN NHIÊN KÌ THÚ</t>
+          <t>Học kì II · Chủ điểm 6: Thiên nhiên kì thú</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr"/>
@@ -5822,7 +5822,7 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 6: THIÊN NHIÊN KÌ THÚ</t>
+          <t>Học kì II · Chủ điểm 6: Thiên nhiên kì thú</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr"/>
@@ -5856,7 +5856,7 @@
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 7: THẾ GIỚI TRONG MẮT EM</t>
+          <t>Học kì II · Chủ điểm 7: Thế giới trong mắt em</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr"/>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 7: THẾ GIỚI TRONG MẮT EM</t>
+          <t>Học kì II · Chủ điểm 7: Thế giới trong mắt em</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr"/>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 7: THẾ GIỚI TRONG MẮT EM</t>
+          <t>Học kì II · Chủ điểm 7: Thế giới trong mắt em</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr"/>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 7: THẾ GIỚI TRONG MẮT EM</t>
+          <t>Học kì II · Chủ điểm 7: Thế giới trong mắt em</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr"/>
@@ -5992,7 +5992,7 @@
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 7: THẾ GIỚI TRONG MẮT EM</t>
+          <t>Học kì II · Chủ điểm 7: Thế giới trong mắt em</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr"/>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 7: THẾ GIỚI TRONG MẮT EM</t>
+          <t>Học kì II · Chủ điểm 7: Thế giới trong mắt em</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr"/>
@@ -6060,7 +6060,7 @@
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 7: THẾ GIỚI TRONG MẮT EM</t>
+          <t>Học kì II · Chủ điểm 7: Thế giới trong mắt em</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr"/>
@@ -6094,7 +6094,7 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 7: THẾ GIỚI TRONG MẮT EM</t>
+          <t>Học kì II · Chủ điểm 7: Thế giới trong mắt em</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr"/>
@@ -6128,7 +6128,7 @@
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 7: THẾ GIỚI TRONG MẮT EM</t>
+          <t>Học kì II · Chủ điểm 7: Thế giới trong mắt em</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr"/>
@@ -6162,7 +6162,7 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 7: THẾ GIỚI TRONG MẮT EM</t>
+          <t>Học kì II · Chủ điểm 7: Thế giới trong mắt em</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr"/>
@@ -6196,7 +6196,7 @@
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 8: ĐẤT NƯỚC VÀ CON NGƯỜI</t>
+          <t>Học kì II · Chủ điểm 8: Đất nước và con người</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr"/>
@@ -6231,7 +6231,7 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 8: ĐẤT NƯỚC VÀ CON NGƯỜI</t>
+          <t>Học kì II · Chủ điểm 8: Đất nước và con người</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr"/>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 8: ĐẤT NƯỚC VÀ CON NGƯỜI</t>
+          <t>Học kì II · Chủ điểm 8: Đất nước và con người</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr"/>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 8: ĐẤT NƯỚC VÀ CON NGƯỜI</t>
+          <t>Học kì II · Chủ điểm 8: Đất nước và con người</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr"/>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 8: ĐẤT NƯỚC VÀ CON NGƯỜI</t>
+          <t>Học kì II · Chủ điểm 8: Đất nước và con người</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr"/>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 8: ĐẤT NƯỚC VÀ CON NGƯỜI</t>
+          <t>Học kì II · Chủ điểm 8: Đất nước và con người</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr"/>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 8: ĐẤT NƯỚC VÀ CON NGƯỜI</t>
+          <t>Học kì II · Chủ điểm 8: Đất nước và con người</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr"/>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 8: ĐẤT NƯỚC VÀ CON NGƯỜI</t>
+          <t>Học kì II · Chủ điểm 8: Đất nước và con người</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr"/>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>HỌC KÌ II · Chủ điểm 8: ĐẤT NƯỚC VÀ CON NGƯỜI</t>
+          <t>Học kì II · Chủ điểm 8: Đất nước và con người</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr"/>
@@ -6502,7 +6502,7 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>ÔN TẬP CUỐI NĂM</t>
+          <t>Ôn tập cuối năm</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr"/>
@@ -6536,7 +6536,7 @@
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>ÔN TẬP CUỐI NĂM</t>
+          <t>Ôn tập cuối năm</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr"/>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>ÔN TẬP CUỐI NĂM</t>
+          <t>Ôn tập cuối năm</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr"/>
@@ -6604,7 +6604,7 @@
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>ÔN TẬP CUỐI NĂM</t>
+          <t>Ôn tập cuối năm</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr"/>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>ÔN TẬP CUỐI NĂM</t>
+          <t>Ôn tập cuối năm</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr"/>
@@ -10098,7 +10098,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>CĐ 1: TỰ CHĂM SÓC</t>
+          <t>CĐ 1: Tự chăm sóc</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr"/>
@@ -10133,7 +10133,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>CĐ 1: TỰ CHĂM SÓC</t>
+          <t>CĐ 1: Tự chăm sóc</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr"/>
@@ -10168,7 +10168,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>CĐ 1: TỰ CHĂM SÓC</t>
+          <t>CĐ 1: Tự chăm sóc</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr"/>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>CĐ 1: TỰ CHĂM SÓC</t>
+          <t>CĐ 1: Tự chăm sóc</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr"/>
@@ -10239,7 +10239,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CĐ 2: YÊU THƯƠNG</t>
+          <t>CĐ 2: Yêu thương</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr"/>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>CĐ 2: YÊU THƯƠNG</t>
+          <t>CĐ 2: Yêu thương</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CĐ 3: QUAN TÂM CHĂM SÓC NGƯỜI THÂN TRONG GIA ĐÌNH</t>
+          <t>CĐ 3: Quan tâm chăm sóc người thân trong gia đình</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr"/>
@@ -10342,7 +10342,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>CĐ 3: QUAN TÂM CHĂM SÓC NGƯỜI THÂN TRONG GIA ĐÌNH</t>
+          <t>CĐ 3: Quan tâm chăm sóc người thân trong gia đình</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr"/>
@@ -10376,7 +10376,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CĐ 3: QUAN TÂM CHĂM SÓC NGƯỜI THÂN TRONG GIA ĐÌNH</t>
+          <t>CĐ 3: Quan tâm chăm sóc người thân trong gia đình</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr"/>
@@ -10410,7 +10410,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>CĐ 3: QUAN TÂM CHĂM SÓC NGƯỜI THÂN TRONG GIA ĐÌNH</t>
+          <t>CĐ 3: Quan tâm chăm sóc người thân trong gia đình</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr"/>
@@ -10445,7 +10445,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CĐ 3: QUAN TÂM CHĂM SÓC NGƯỜI THÂN TRONG GIA ĐÌNH</t>
+          <t>CĐ 3: Quan tâm chăm sóc người thân trong gia đình</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr"/>
@@ -10475,7 +10475,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>CĐ4: THỰC HIỆN NỘI QUY TRƯỜNG LỚP</t>
+          <t>CĐ4: Thực hiện nội quy trường lớp</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr"/>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CĐ4: THỰC HIỆN NỘI QUY TRƯỜNG LỚP</t>
+          <t>CĐ4: Thực hiện nội quy trường lớp</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr"/>
@@ -10545,7 +10545,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>CĐ4: THỰC HIỆN NỘI QUY TRƯỜNG LỚP</t>
+          <t>CĐ4: Thực hiện nội quy trường lớp</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr"/>
@@ -10582,7 +10582,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CĐ4: THỰC HIỆN NỘI QUY TRƯỜNG LỚP</t>
+          <t>CĐ4: Thực hiện nội quy trường lớp</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr"/>
@@ -10618,7 +10618,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>CĐ4: THỰC HIỆN NỘI QUY TRƯỜNG LỚP</t>
+          <t>CĐ4: Thực hiện nội quy trường lớp</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr"/>
@@ -10654,7 +10654,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CĐ 5: SINH HOẠT NỀN NẾP</t>
+          <t>CĐ 5: Sinh hoạt nền nếp</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr"/>
@@ -10690,7 +10690,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>CĐ 5: SINH HOẠT NỀN NẾP</t>
+          <t>CĐ 5: Sinh hoạt nền nếp</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr"/>
@@ -10724,7 +10724,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CĐ 5: SINH HOẠT NỀN NẾP</t>
+          <t>CĐ 5: Sinh hoạt nền nếp</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr"/>
@@ -10759,7 +10759,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>CĐ 6: TỰ GIÁC LÀM VIỆC CỦA MÌNH</t>
+          <t>CĐ 6: Tự giác làm việc của mình</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr"/>
@@ -10794,7 +10794,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CĐ 6: TỰ GIÁC LÀM VIỆC CỦA MÌNH</t>
+          <t>CĐ 6: Tự giác làm việc của mình</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr"/>
@@ -10830,7 +10830,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>CĐ 6: TỰ GIÁC LÀM VIỆC CỦA MÌNH</t>
+          <t>CĐ 6: Tự giác làm việc của mình</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr"/>
@@ -10866,7 +10866,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>CĐ 7: THẬT THÀ</t>
+          <t>CĐ 7: Thật thà</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr"/>
@@ -10901,7 +10901,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>CĐ 7: THẬT THÀ</t>
+          <t>CĐ 7: Thật thà</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr"/>
@@ -10935,7 +10935,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>CĐ 7: THẬT THÀ</t>
+          <t>CĐ 7: Thật thà</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr"/>
@@ -10969,7 +10969,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>CĐ 7: THẬT THÀ</t>
+          <t>CĐ 7: Thật thà</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr"/>
@@ -11004,7 +11004,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>CĐ 7: THẬT THÀ</t>
+          <t>CĐ 7: Thật thà</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr"/>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>CĐ 8: PHÒNG TRÁNH TAI NẠN, THƯƠNG TÍCH</t>
+          <t>CĐ 8: Phòng tránh tai nạn, thương tích</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr"/>
@@ -11069,7 +11069,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>CĐ 8: PHÒNG TRÁNH TAI NẠN, THƯƠNG TÍCH</t>
+          <t>CĐ 8: Phòng tránh tai nạn, thương tích</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr"/>
@@ -11103,7 +11103,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>CĐ 8: PHÒNG TRÁNH TAI NẠN, THƯƠNG TÍCH</t>
+          <t>CĐ 8: Phòng tránh tai nạn, thương tích</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr"/>
@@ -11137,7 +11137,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>CĐ 8: PHÒNG TRÁNH TAI NẠN, THƯƠNG TÍCH</t>
+          <t>CĐ 8: Phòng tránh tai nạn, thương tích</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr"/>
@@ -11171,7 +11171,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>CĐ 8: PHÒNG TRÁNH TAI NẠN, THƯƠNG TÍCH</t>
+          <t>CĐ 8: Phòng tránh tai nạn, thương tích</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr"/>
@@ -11205,7 +11205,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>CĐ 8: PHÒNG TRÁNH TAI NẠN, THƯƠNG TÍCH</t>
+          <t>CĐ 8: Phòng tránh tai nạn, thương tích</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>CĐ 8: PHÒNG TRÁNH TAI NẠN, THƯƠNG TÍCH</t>
+          <t>CĐ 8: Phòng tránh tai nạn, thương tích</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr"/>
@@ -11275,7 +11275,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>CĐ 8: PHÒNG TRÁNH TAI NẠN, THƯƠNG TÍCH</t>
+          <t>CĐ 8: Phòng tránh tai nạn, thương tích</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr"/>
@@ -18508,7 +18508,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 1: CHÀO NĂM HỌC MỚI</t>
+          <t>Chủ đề 1: Chào năm học mới</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr"/>
@@ -18538,7 +18538,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 1: CHÀO NĂM HỌC MỚI</t>
+          <t>Chủ đề 1: Chào năm học mới</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr"/>
@@ -18572,7 +18572,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 1: CHÀO NĂM HỌC MỚI</t>
+          <t>Chủ đề 1: Chào năm học mới</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr"/>
@@ -18606,7 +18606,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 1: CHÀO NĂM HỌC MỚI</t>
+          <t>Chủ đề 1: Chào năm học mới</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr"/>
@@ -18641,7 +18641,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 1: CHÀO NĂM HỌC MỚI</t>
+          <t>Chủ đề 1: Chào năm học mới</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr"/>
@@ -18675,7 +18675,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 1: CHÀO NĂM HỌC MỚI</t>
+          <t>Chủ đề 1: Chào năm học mới</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 1: CHÀO NĂM HỌC MỚI</t>
+          <t>Chủ đề 1: Chào năm học mới</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr"/>
@@ -18741,7 +18741,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 1: CHÀO NĂM HỌC MỚI</t>
+          <t>Chủ đề 1: Chào năm học mới</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr"/>
@@ -18775,7 +18775,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 1: CHÀO NĂM HỌC MỚI</t>
+          <t>Chủ đề 1: Chào năm học mới</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr"/>
@@ -18810,7 +18810,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 1: CHÀO NĂM HỌC MỚI</t>
+          <t>Chủ đề 1: Chào năm học mới</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr"/>
@@ -18840,7 +18840,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 1: CHÀO NĂM HỌC MỚI</t>
+          <t>Chủ đề 1: Chào năm học mới</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr"/>
@@ -18874,7 +18874,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 1: CHÀO NĂM HỌC MỚI</t>
+          <t>Chủ đề 1: Chào năm học mới</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr"/>
@@ -18909,7 +18909,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 2: EM BIẾT YÊU THƯƠNG</t>
+          <t>Chủ đề 2: Em biết yêu thương</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr"/>
@@ -18939,7 +18939,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 2: EM BIẾT YÊU THƯƠNG</t>
+          <t>Chủ đề 2: Em biết yêu thương</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr"/>
@@ -18974,7 +18974,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 2: EM BIẾT YÊU THƯƠNG</t>
+          <t>Chủ đề 2: Em biết yêu thương</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr"/>
@@ -19008,7 +19008,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 2: EM BIẾT YÊU THƯƠNG</t>
+          <t>Chủ đề 2: Em biết yêu thương</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr"/>
@@ -19038,7 +19038,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 2: EM BIẾT YÊU THƯƠNG</t>
+          <t>Chủ đề 2: Em biết yêu thương</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr"/>
@@ -19072,7 +19072,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 2: EM BIẾT YÊU THƯƠNG</t>
+          <t>Chủ đề 2: Em biết yêu thương</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr"/>
@@ -19107,7 +19107,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 2: EM BIẾT YÊU THƯƠNG</t>
+          <t>Chủ đề 2: Em biết yêu thương</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr"/>
@@ -19137,7 +19137,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 2: EM BIẾT YÊU THƯƠNG</t>
+          <t>Chủ đề 2: Em biết yêu thương</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr"/>
@@ -19171,7 +19171,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 2: EM BIẾT YÊU THƯƠNG</t>
+          <t>Chủ đề 2: Em biết yêu thương</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr"/>
@@ -19205,7 +19205,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 2: EM BIẾT YÊU THƯƠNG</t>
+          <t>Chủ đề 2: Em biết yêu thương</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr"/>
@@ -19239,7 +19239,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 2: EM BIẾT YÊU THƯƠNG</t>
+          <t>Chủ đề 2: Em biết yêu thương</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr"/>
@@ -19273,7 +19273,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 2: EM BIẾT YÊU THƯƠNG</t>
+          <t>Chủ đề 2: Em biết yêu thương</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr"/>
@@ -19308,7 +19308,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 3: TRUYỀN THỐNG TRƯỜNG EM</t>
+          <t>Chủ đề 3: Truyền thống trường em</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr"/>
@@ -19343,7 +19343,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 3: TRUYỀN THỐNG TRƯỜNG EM</t>
+          <t>Chủ đề 3: Truyền thống trường em</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr"/>
@@ -19378,7 +19378,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 3: TRUYỀN THỐNG TRƯỜNG EM</t>
+          <t>Chủ đề 3: Truyền thống trường em</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr"/>
@@ -19412,7 +19412,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 3: TRUYỀN THỐNG TRƯỜNG EM</t>
+          <t>Chủ đề 3: Truyền thống trường em</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr"/>
@@ -19446,7 +19446,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 3: TRUYỀN THỐNG TRƯỜNG EM</t>
+          <t>Chủ đề 3: Truyền thống trường em</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr"/>
@@ -19480,7 +19480,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 3: TRUYỀN THỐNG TRƯỜNG EM</t>
+          <t>Chủ đề 3: Truyền thống trường em</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr"/>
@@ -19515,7 +19515,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 3: TRUYỀN THỐNG TRƯỜNG EM</t>
+          <t>Chủ đề 3: Truyền thống trường em</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr"/>
@@ -19545,7 +19545,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 3: TRUYỀN THỐNG TRƯỜNG EM</t>
+          <t>Chủ đề 3: Truyền thống trường em</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr"/>
@@ -19579,7 +19579,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 3: TRUYỀN THỐNG TRƯỜNG EM</t>
+          <t>Chủ đề 3: Truyền thống trường em</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr"/>
@@ -19613,7 +19613,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 3: TRUYỀN THỐNG TRƯỜNG EM</t>
+          <t>Chủ đề 3: Truyền thống trường em</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr"/>
@@ -19648,7 +19648,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 3: TRUYỀN THỐNG TRƯỜNG EM</t>
+          <t>Chủ đề 3: Truyền thống trường em</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr"/>
@@ -19682,7 +19682,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 3: TRUYỀN THỐNG TRƯỜNG EM</t>
+          <t>Chủ đề 3: Truyền thống trường em</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr"/>
@@ -19717,7 +19717,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 4: AN TOÀN CHO EM</t>
+          <t>Chủ đề 4: An toàn cho em</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr"/>
@@ -19752,7 +19752,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 4: AN TOÀN CHO EM</t>
+          <t>Chủ đề 4: An toàn cho em</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr"/>
@@ -19787,7 +19787,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 4: AN TOÀN CHO EM</t>
+          <t>Chủ đề 4: An toàn cho em</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr"/>
@@ -19817,7 +19817,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 4: AN TOÀN CHO EM</t>
+          <t>Chủ đề 4: An toàn cho em</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr"/>
@@ -19847,7 +19847,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 4: AN TOÀN CHO EM</t>
+          <t>Chủ đề 4: An toàn cho em</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr"/>
@@ -19882,7 +19882,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 4: AN TOÀN CHO EM</t>
+          <t>Chủ đề 4: An toàn cho em</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr"/>
@@ -19916,7 +19916,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 4: AN TOÀN CHO EM</t>
+          <t>Chủ đề 4: An toàn cho em</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr"/>
@@ -19946,7 +19946,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 4: AN TOÀN CHO EM</t>
+          <t>Chủ đề 4: An toàn cho em</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr"/>
@@ -19981,7 +19981,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 4: AN TOÀN CHO EM</t>
+          <t>Chủ đề 4: An toàn cho em</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr"/>
@@ -20011,7 +20011,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 4: AN TOÀN CHO EM</t>
+          <t>Chủ đề 4: An toàn cho em</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr"/>
@@ -20045,7 +20045,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 4: AN TOÀN CHO EM</t>
+          <t>Chủ đề 4: An toàn cho em</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr"/>
@@ -20080,7 +20080,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 4: AN TOÀN CHO EM</t>
+          <t>Chủ đề 4: An toàn cho em</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr"/>
@@ -20115,7 +20115,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 5: EM QUÝ TRỌNG BẢN THÂN</t>
+          <t>Chủ đề 5: Em quý trọng bản thân</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr"/>
@@ -20149,7 +20149,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 5: EM QUÝ TRỌNG BẢN THÂN</t>
+          <t>Chủ đề 5: Em quý trọng bản thân</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr"/>
@@ -20183,7 +20183,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 5: EM QUÝ TRỌNG BẢN THÂN</t>
+          <t>Chủ đề 5: Em quý trọng bản thân</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr"/>
@@ -20213,7 +20213,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 5: EM QUÝ TRỌNG BẢN THÂN</t>
+          <t>Chủ đề 5: Em quý trọng bản thân</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr"/>
@@ -20243,7 +20243,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 5: EM QUÝ TRỌNG BẢN THÂN</t>
+          <t>Chủ đề 5: Em quý trọng bản thân</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr"/>
@@ -20277,7 +20277,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 5: EM QUÝ TRỌNG BẢN THÂN</t>
+          <t>Chủ đề 5: Em quý trọng bản thân</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr"/>
@@ -20312,7 +20312,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 5: EM QUÝ TRỌNG BẢN THÂN</t>
+          <t>Chủ đề 5: Em quý trọng bản thân</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr"/>
@@ -20342,7 +20342,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 5: EM QUÝ TRỌNG BẢN THÂN</t>
+          <t>Chủ đề 5: Em quý trọng bản thân</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr"/>
@@ -20376,7 +20376,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 5: EM QUÝ TRỌNG BẢN THÂN</t>
+          <t>Chủ đề 5: Em quý trọng bản thân</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr"/>
@@ -20406,7 +20406,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 5: EM QUÝ TRỌNG BẢN THÂN</t>
+          <t>Chủ đề 5: Em quý trọng bản thân</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr"/>
@@ -20440,7 +20440,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 5: EM QUÝ TRỌNG BẢN THÂN</t>
+          <t>Chủ đề 5: Em quý trọng bản thân</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr"/>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 5: EM QUÝ TRỌNG BẢN THÂN</t>
+          <t>Chủ đề 5: Em quý trọng bản thân</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr"/>
@@ -20509,7 +20509,7 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 6: VUI ĐÓN MÙA XUÂN</t>
+          <t>Chủ đề 6: Vui đón mùa xuân</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr"/>
@@ -20539,7 +20539,7 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 6: VUI ĐÓN MÙA XUÂN</t>
+          <t>Chủ đề 6: Vui đón mùa xuân</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr"/>
@@ -20573,7 +20573,7 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 6: VUI ĐÓN MÙA XUÂN</t>
+          <t>Chủ đề 6: Vui đón mùa xuân</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr"/>
@@ -20607,7 +20607,7 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 6: VUI ĐÓN MÙA XUÂN</t>
+          <t>Chủ đề 6: Vui đón mùa xuân</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr"/>
@@ -20637,7 +20637,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 6: VUI ĐÓN MÙA XUÂN</t>
+          <t>Chủ đề 6: Vui đón mùa xuân</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr"/>
@@ -20671,7 +20671,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 6: VUI ĐÓN MÙA XUÂN</t>
+          <t>Chủ đề 6: Vui đón mùa xuân</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr"/>
@@ -20707,7 +20707,7 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 6: VUI ĐÓN MÙA XUÂN</t>
+          <t>Chủ đề 6: Vui đón mùa xuân</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr"/>
@@ -20741,7 +20741,7 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 6: VUI ĐÓN MÙA XUÂN</t>
+          <t>Chủ đề 6: Vui đón mùa xuân</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr"/>
@@ -20775,7 +20775,7 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 6: VUI ĐÓN MÙA XUÂN</t>
+          <t>Chủ đề 6: Vui đón mùa xuân</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr"/>
@@ -20809,7 +20809,7 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 6: VUI ĐÓN MÙA XUÂN</t>
+          <t>Chủ đề 6: Vui đón mùa xuân</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr"/>
@@ -20839,7 +20839,7 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 6: VUI ĐÓN MÙA XUÂN</t>
+          <t>Chủ đề 6: Vui đón mùa xuân</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr"/>
@@ -20873,7 +20873,7 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 6: VUI ĐÓN MÙA XUÂN</t>
+          <t>Chủ đề 6: Vui đón mùa xuân</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr"/>
@@ -20909,7 +20909,7 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 7: THAM GIA HOẠT ĐỘNG CỘNG ĐỒNG</t>
+          <t>Chủ đề 7: Tham gia hoạt động cộng đồng</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr"/>
@@ -20944,7 +20944,7 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 7: THAM GIA HOẠT ĐỘNG CỘNG ĐỒNG</t>
+          <t>Chủ đề 7: Tham gia hoạt động cộng đồng</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr"/>
@@ -20979,7 +20979,7 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 7: THAM GIA HOẠT ĐỘNG CỘNG ĐỒNG</t>
+          <t>Chủ đề 7: Tham gia hoạt động cộng đồng</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr"/>
@@ -21009,7 +21009,7 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 7: THAM GIA HOẠT ĐỘNG CỘNG ĐỒNG</t>
+          <t>Chủ đề 7: Tham gia hoạt động cộng đồng</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr"/>
@@ -21043,7 +21043,7 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 7: THAM GIA HOẠT ĐỘNG CỘNG ĐỒNG</t>
+          <t>Chủ đề 7: Tham gia hoạt động cộng đồng</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr"/>
@@ -21077,7 +21077,7 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 7: THAM GIA HOẠT ĐỘNG CỘNG ĐỒNG</t>
+          <t>Chủ đề 7: Tham gia hoạt động cộng đồng</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr"/>
@@ -21107,7 +21107,7 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 7: THAM GIA HOẠT ĐỘNG CỘNG ĐỒNG</t>
+          <t>Chủ đề 7: Tham gia hoạt động cộng đồng</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr"/>
@@ -21137,7 +21137,7 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 7: THAM GIA HOẠT ĐỘNG CỘNG ĐỒNG</t>
+          <t>Chủ đề 7: Tham gia hoạt động cộng đồng</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr"/>
@@ -21171,7 +21171,7 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 7: THAM GIA HOẠT ĐỘNG CỘNG ĐỒNG</t>
+          <t>Chủ đề 7: Tham gia hoạt động cộng đồng</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr"/>
@@ -21201,7 +21201,7 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 7: THAM GIA HOẠT ĐỘNG CỘNG ĐỒNG</t>
+          <t>Chủ đề 7: Tham gia hoạt động cộng đồng</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr"/>
@@ -21231,7 +21231,7 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 7: THAM GIA HOẠT ĐỘNG CỘNG ĐỒNG</t>
+          <t>Chủ đề 7: Tham gia hoạt động cộng đồng</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr"/>
@@ -21265,7 +21265,7 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 7: THAM GIA HOẠT ĐỘNG CỘNG ĐỒNG</t>
+          <t>Chủ đề 7: Tham gia hoạt động cộng đồng</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr"/>
@@ -21300,7 +21300,7 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 8: QUÊ HƯƠNG TƯƠI ĐẸP</t>
+          <t>Chủ đề 8: Quê hương tươi đẹp</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr"/>
@@ -21334,7 +21334,7 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 8: QUÊ HƯƠNG TƯƠI ĐẸP</t>
+          <t>Chủ đề 8: Quê hương tươi đẹp</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr"/>
@@ -21368,7 +21368,7 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 8: QUÊ HƯƠNG TƯƠI ĐẸP</t>
+          <t>Chủ đề 8: Quê hương tươi đẹp</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr"/>
@@ -21402,7 +21402,7 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 8: QUÊ HƯƠNG TƯƠI ĐẸP</t>
+          <t>Chủ đề 8: Quê hương tươi đẹp</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr"/>
@@ -21432,7 +21432,7 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 8: QUÊ HƯƠNG TƯƠI ĐẸP</t>
+          <t>Chủ đề 8: Quê hương tươi đẹp</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr"/>
@@ -21466,7 +21466,7 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 8: QUÊ HƯƠNG TƯƠI ĐẸP</t>
+          <t>Chủ đề 8: Quê hương tươi đẹp</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr"/>
@@ -21502,7 +21502,7 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 8: QUÊ HƯƠNG TƯƠI ĐẸP</t>
+          <t>Chủ đề 8: Quê hương tươi đẹp</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr"/>
@@ -21537,7 +21537,7 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 8: QUÊ HƯƠNG TƯƠI ĐẸP</t>
+          <t>Chủ đề 8: Quê hương tươi đẹp</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr"/>
@@ -21572,7 +21572,7 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 8: QUÊ HƯƠNG TƯƠI ĐẸP</t>
+          <t>Chủ đề 8: Quê hương tươi đẹp</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr"/>
@@ -21606,7 +21606,7 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 8: QUÊ HƯƠNG TƯƠI ĐẸP</t>
+          <t>Chủ đề 8: Quê hương tươi đẹp</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr"/>
@@ -21640,7 +21640,7 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 8: QUÊ HƯƠNG TƯƠI ĐẸP</t>
+          <t>Chủ đề 8: Quê hương tươi đẹp</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr"/>
@@ -21675,7 +21675,7 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 8: QUÊ HƯƠNG TƯƠI ĐẸP</t>
+          <t>Chủ đề 8: Quê hương tươi đẹp</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr"/>
@@ -21711,7 +21711,7 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 9: EM BẢO VỆ MÔI TRƯỜNG</t>
+          <t>Chủ đề 9: Em bảo vệ môi trường</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr"/>
@@ -21745,7 +21745,7 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 9: EM BẢO VỆ MÔI TRƯỜNG</t>
+          <t>Chủ đề 9: Em bảo vệ môi trường</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr"/>
@@ -21781,7 +21781,7 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 9: EM BẢO VỆ MÔI TRƯỜNG</t>
+          <t>Chủ đề 9: Em bảo vệ môi trường</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr"/>
@@ -21816,7 +21816,7 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 9: EM BẢO VỆ MÔI TRƯỜNG</t>
+          <t>Chủ đề 9: Em bảo vệ môi trường</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr"/>
@@ -21846,7 +21846,7 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 9: EM BẢO VỆ MÔI TRƯỜNG</t>
+          <t>Chủ đề 9: Em bảo vệ môi trường</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr"/>
@@ -21882,7 +21882,7 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 9: EM BẢO VỆ MÔI TRƯỜNG</t>
+          <t>Chủ đề 9: Em bảo vệ môi trường</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr"/>
@@ -21918,7 +21918,7 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 9: EM BẢO VỆ MÔI TRƯỜNG</t>
+          <t>Chủ đề 9: Em bảo vệ môi trường</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr"/>
@@ -21952,7 +21952,7 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 9: EM BẢO VỆ MÔI TRƯỜNG</t>
+          <t>Chủ đề 9: Em bảo vệ môi trường</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr"/>
@@ -21987,7 +21987,7 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 9: EM BẢO VỆ MÔI TRƯỜNG</t>
+          <t>Chủ đề 9: Em bảo vệ môi trường</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr"/>
